--- a/stuora-growth-playbook.xlsx
+++ b/stuora-growth-playbook.xlsx
@@ -1284,7 +1284,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>• Offer to host an AmCham “Business After Hours” / LPVA networking night at the bar.
+          <t>• Offer to host an AmCham “Business After Hours” networking night at the bar.
 • They bring the audience; you show the venue.
 • Later, join the one chamber closest to your target.</t>
         </is>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>53.5% of Riga speaks Russian at home — half of your local audience. Reach them without Yandex: Google works, plus Russian-language listings and creators.</t>
+          <t>53.5% of Rigans are native Russian speakers — about half your local audience. Reach them without Yandex: Google works, plus Russian-language listings and creators.</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Elite international recognition. Europe's 50 Best 2026 has already launched (no Baltic bar yet) — a play for future editions. Their free 50 Best Discovery directory (where Riga's nosaints &amp; Gimlet already appear) works the same way: earned by Academy votes, not applied for.</t>
+          <t>Elite international recognition. Europe's 50 Best 2026 has already launched (no Baltic bar yet) — a play for future editions. Their free 50 Best Discovery directory (where Riga's Gimlet already appears) works the same way: earned by Academy votes, not applied for.</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">

--- a/stuora-growth-playbook.xlsx
+++ b/stuora-growth-playbook.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1130,33 +1130,75 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t>Untapped &amp; high-traffic</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>RestaurantGuru</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>tourists / locals</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>A 20M+ visits/month bar &amp; restaurant aggregator (pulls from Google, Yelp, Foursquare). Stuora’s page already exists — auto-built from your Google data, but unclaimed. Claiming is free and lets you fix photos/hours and reply to reviews.</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>• Open Stuora’s existing page and use “Claim your business”.
+• Confirm a free business account to verify ownership.
+• Fix photos, hours &amp; description; reply to reviews.</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Open &amp; claim your listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
           <t>For corporate clients</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>corporate</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>Free</t>
         </is>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="E20" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>The main B2B channel — every decision-maker (HR, office managers, EAs, event managers) is here. Your most direct line to corporate clients.</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>• Create a Stuora Company Page + a strong personal profile.
 • Direct-message HR / People &amp; Culture / Office Manager / EA roles at target Riga firms (IT, fintech, consulting).
@@ -1164,875 +1206,875 @@
 • Join Latvian HR &amp; business groups.</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>Create a Company Page</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>For corporate clients</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Event &amp; DMC agencies</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>corporate</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>Free + paid</t>
         </is>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E21" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Agencies package events for corporate clients and pick the venue. One good partner = a steady flow of orders with zero marketing spend.</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>• Prepare a 1-page trade sheet (formats, capacity, net prices, photos).
 • Contact 5–8 Riga event / DMC agencies; offer a free “fam visit” mini-class.
 • Agree referral terms.</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>Riga agencies list</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>For corporate clients</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Meet Rīga (MICE)</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>corporate</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>Free</t>
         </is>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="E22" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Riga's official convention bureau — a supplier registry connecting event organizers with local venues. Inbound MICE &amp; after-conference leads.</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>• Apply to be listed as a venue / activity supplier.
 • Position Stuora for receptions &amp; team activities.</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>Get listed</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>For corporate clients</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Business chambers (AmCham &amp; co.)</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>corporate</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Free + paid</t>
         </is>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E23" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Communities of exactly the decision-makers you want. AmCham's “Business After Hours” lets a member host peers on-site — a perfect showcase.</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>• Offer to host an AmCham “Business After Hours” networking night at the bar.
 • They bring the audience; you show the venue.
 • Later, join the one chamber closest to your target.</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>AmCham Latvia</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>For corporate clients</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Coworkings &amp; startup hubs</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>corporate</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>Free</t>
         </is>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="E24" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>Where startup &amp; IT teams concentrate — the crowd that books offbeat team-building.</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>• Offer residents a perk (promo class / first-booking discount).
 • Host one demo evening for the community manager &amp; residents.
 • Leave a flyer / QR.</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>Startup House Riga</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>For corporate clients</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>HR communities (LPVA)</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>corporate</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>Free + paid</t>
         </is>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="E25" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>The people who actually decide on team-building. Get in front of them directly.</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>• Offer LPVA to host their afterparty / networking at Stuora.
 • Speak at or sponsor an HR event with a mini-tasting.</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>LPVA events</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>For corporate clients</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Experience-gift shops</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>corporate</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>Free</t>
         </is>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="E26" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>Gift-experience shops where companies buy team activities as vouchers — a place to be listed for inbound corporate leads.</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>• List your masterclass on experience-gift shops such as Dāvanu Serviss.
 • Note: Weasgley (weasgley.com) and Ballītes.lv are event organizers (competitors), not open directories — approach them only as a subcontracting partner who can send you groups.</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>Dāvanu Serviss (business)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>For corporate clients</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Eventbrite / Meetup showcase</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>corporate</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>Free + paid</t>
         </is>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="E27" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>Run an open “Cocktail Thursday” as a shop-window: HR people test the format before booking, and you collect photos &amp; reviews.</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>• Publish an open masterclass on a free weeknight via Eventbrite.
 • Invite Riga Meetup groups (Startup House, ProductTank) to host at the bar.</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>Create an event</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>For corporate clients</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Hotels &amp; conference venues</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>corporate</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>Free</t>
         </is>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="E28" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>Old Town hotels host congresses &amp; business groups needing an atmospheric after-conference reception nearby — that's you.</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>• Reach event coordinators at central / Old Town hotels for a referral deal.
 • Via Meet Rīga, reach congress organizers.</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>Map Old Town hotels</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Locals, social &amp; press</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Micro-influencers (Riga)</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>tourists / locals</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>Free + paid</t>
         </is>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E29" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>Get local food &amp; drink creators to post about the bar — reaches both locals and tourists, and gives you content.</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>• Find Riga food/drink micro-bloggers (search #rigabars, the Audēju geotag) and invite them for a barter — drinks for a Reel.
 • Or hire directly on Collabstr.</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>Browse Riga creators</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Locals, social &amp; press</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>LIAA press &amp; blogger trips</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>tourists</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>Free</t>
         </is>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="E30" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>The state agency invites and funds a limited number of journalist/influencer visits — you can be a stop on the route.</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>• Pitch via the Media Request / Influencer Request form.
 • Offer a themed story angle; approval isn't guaranteed.</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>Pitch LIAA</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Locals, social &amp; press</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Reach Russian-speaking Rigans</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>locals</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>Free</t>
         </is>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="E31" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>53.5% of Rigans are native Russian speakers — about half your local audience. Reach them without Yandex: Google works, plus Russian-language listings and creators.</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>• Post events on Russian-language what's-on sites: afishamira.com, meeting.lv/afisha, rus.tvnet.lv, rus.delfi.lv.
 • Publish bilingual posts (LV / RU / EN).
 • Invite Russian-speaking Riga micro-bloggers (barter).</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>Afisha Mira · Riga</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Locals, social &amp; press</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Facebook (events &amp; locals)</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>locals</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>Free</t>
         </is>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="E32" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>Still where locals 35+ and Russian-speaking Rigans find what's on. Good for event reach and community.</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>• Keep a Facebook Page with an event for every quiz / tasting / guest shift.
 • Cross-post from Instagram; join Riga what's-on groups.</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>Create a Page</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Partnerships &amp; foot traffic</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Escape Room Riga</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>tourists / locals</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>Free</t>
         </is>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="E33" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>A big operator selling corporate/team events — natural “after the quest, drinks at Stuora”. Also fills your private Mon–Wed.</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>• Propose a “quest → cocktails” package + a group promo code.
 • Offer to host their corporate groups on Mon–Wed.</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>Contact Escape Room</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Partnerships &amp; foot traffic</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Pub-quiz night</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>locals</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>Free</t>
         </is>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="E34" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>A recurring weekday quiz brings a steady local crowd — and gets you onto Riga's quiz aggregator.</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>• Run a weekly quiz (e.g. a private Tue slot).
 • Get listed on the Riga quiz agenda (Extrareality).</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>See quiz agenda</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Partnerships &amp; foot traffic</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Hotel concierges</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>tourists</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>Free</t>
         </is>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="E35" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>A concierge is a human recommendation engine — and you're a 5-minute walk from dozens of them. Best target: boutique hotels with NO bar of their own.</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>• Walk the 10-minute radius; meet concierges in person.
 • Leave beautiful map-cards (entrance is hard to find).
 • Offer a welcome-drink on presentation of the card.</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>Map nearby hotels</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Partnerships &amp; foot traffic</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>Cruise tourism</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>tourists</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>Free</t>
         </is>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="E36" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>2025 hit a record 85 ships / 115,500 passengers, and the Old Town is a 15-min walk from the terminal — a big daytime, high-spend flow.</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>• Offer daytime tasting slots timed to ship calls.
 • Get into shore-excursion operators' recommendations.</t>
         </is>
       </c>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>Riga port · passengers</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Partnerships &amp; foot traffic</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>Alcohol-brand co-branding</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>tourists / locals</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>Free + paid</t>
         </is>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="E37" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>Brands often supply product or co-fund events for placement + posts. Build a signature cocktail around a Latvian icon.</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>• Design a signature cocktail on Riga Black Balsam or a local distillery spirit.
 • Pitch a joint event / tasting to their marketing team.</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
+      <c r="H37" s="4" t="inlineStr">
         <is>
           <t>No single sign-up — reach brand reps directly.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Awards &amp; recognition</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Europe's / World's 50 Best Bars</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>tourists / locals</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>Free</t>
         </is>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="E38" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>Elite international recognition. Europe's 50 Best 2026 has already launched (no Baltic bar yet) — a play for future editions. Their free 50 Best Discovery directory (where Riga's Gimlet already appears) works the same way: earned by Academy votes, not applied for.</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>• Host industry peers and guest shifts to get on voters' radar.
 • Take part in Baltic bar events; let the work be seen.</t>
         </is>
       </c>
-      <c r="H37" s="7" t="inlineStr">
+      <c r="H38" s="7" t="inlineStr">
         <is>
           <t>How voting works</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Awards &amp; recognition</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Baltic Wine &amp; Drinks Awards</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>tourists / locals</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>Paid</t>
         </is>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="E39" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>Regional award covering Latvia/Estonia/Lithuania — a Riga cocktail bar (Mākonis) was a 2025 highlight.</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>• Watch for the entry window and submit.
 • Line up your award-worthy menu highlights.</t>
         </is>
       </c>
-      <c r="H38" s="7" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>Read 2025 results</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Awards &amp; recognition</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>Industry events &amp; comps</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>tourists / locals</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>Free + paid</t>
         </is>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="E40" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>Monin Cup Latvia, Riga Food expo, Star Wine List Baltics — visibility, networking, and a path onto the 50 Best radar.</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>• Enter your bartender in Monin Cup Latvia.
 • Attend / take a stand at Riga Food.</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="H40" s="7" t="inlineStr">
         <is>
           <t>Riga Food expo</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>Optional / your call</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>Yandex Maps</t>
-        </is>
-      </c>
-      <c r="F42" s="10" t="inlineStr">
-        <is>
-          <t>Likely low value — Probably not worth it for Latvia — Russian tourists are visa-restricted until end-2026 and Yandex has been blocked here since Dec 2023 (needs a VPN). Not 100% certain, though: if you specifically want Russian-speaking Rigans (53.5% of the city), it's a minor “maybe” — but Google + Instagram + Russian-language listings reach them better and for free. Verdict: low priority, not forbidden.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>visam.lv</t>
+          <t>Yandex Maps</t>
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>Worth a cheap test — A new Latvian app spending aggressively on advertising and growing fast (top-5 downloads) — a genuinely interesting, high-attention player right now, and people are on it. It's a classifieds board, not a venue directory, so it won't drive “where to drink” discovery — but a low-cost experiment could pay off while attention is high: post your private / corporate-event offer or ticketed events there and see what comes back. Worth watching as it grows.</t>
+          <t>Likely low value — Probably not worth it for Latvia — Russian tourists are visa-restricted until end-2026 and Yandex has been blocked here since Dec 2023 (needs a VPN). Not 100% certain, though: if you specifically want Russian-speaking Rigans (53.5% of the city), it's a minor “maybe” — but Google + Instagram + Russian-language listings reach them better and for free. Verdict: low priority, not forbidden.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="9" t="inlineStr">
         <is>
+          <t>visam.lv</t>
+        </is>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>Worth a cheap test — A new Latvian app spending aggressively on advertising and growing fast (top-5 downloads) — a genuinely interesting, high-attention player right now, and people are on it. It's a classifieds board, not a venue directory, so it won't drive “where to drink” discovery — but a low-cost experiment could pay off while attention is high: post your private / corporate-event offer or ticketed events there and see what comes back. Worth watching as it grows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="9" t="inlineStr">
+        <is>
           <t>Paid “rankings” &amp; guaranteed awards</t>
         </is>
       </c>
-      <c r="F44" s="10" t="inlineStr">
+      <c r="F45" s="10" t="inlineStr">
         <is>
           <t>Genuine caution — This one we're sure about: 50 Best lists can't be applied for or bought, so anyone promising a paid ranking is best avoided. (Also worth knowing: Collabstr isn't fully free — a platform fee applies on top of the creator's price.)</t>
         </is>
@@ -2040,6 +2082,7 @@
     </row>
   </sheetData>
   <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId3"/>
@@ -2054,26 +2097,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stuora-growth-playbook.xlsx
+++ b/stuora-growth-playbook.xlsx
@@ -2376,7 +2376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -2438,99 +2438,106 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>☐  Claim your auto-created RestaurantGuru page</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Weeks 2–4 — free / barter</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>☐  Walk the concierges (hotels without a bar)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>☐  Email 3 pub-crawl operators</t>
+          <t>☐  Walk the concierges (hotels without a bar)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>☐  Partner with Escape Room Riga for Mon–Wed</t>
+          <t>☐  Email 3 pub-crawl operators</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>☐  Pitch a LIAA blog-trip + 3–4 outlets</t>
+          <t>☐  Partner with Escape Room Riga for Mon–Wed</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>☐  Line up 5–10 local micro-bloggers</t>
+          <t>☐  Pitch a LIAA blog-trip + 3–4 outlets</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
+          <t>☐  Line up 5–10 local micro-bloggers</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
           <t>☐  Corporate: LinkedIn outreach + 5 agencies + offer to host AmCham</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Month 2+ — paid / long game</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>☐  List a cocktail masterclass on GetYourGuide + Viator + Airbnb</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>☐  Commission 2–3 Reels</t>
+          <t>☐  List a cocktail masterclass on GetYourGuide + Viator + Airbnb</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>☐  Launch a weekly pub-quiz</t>
+          <t>☐  Commission 2–3 Reels</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>☐  Co-brand with an alcohol brand</t>
+          <t>☐  Launch a weekly pub-quiz</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>☐  Enter Monin Cup / Riga Food; aim at the Europe's 50 Best radar</t>
+          <t>☐  Co-brand with an alcohol brand</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>☐  Enter Monin Cup / Riga Food; aim at the Europe's 50 Best radar</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>☐  Run one open corporate showcase evening</t>
         </is>
